--- a/templates/TATA Capital/TATA_Stockyard_Agency_Template_2026-27.xlsx
+++ b/templates/TATA Capital/TATA_Stockyard_Agency_Template_2026-27.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Rachit Goyal\Downloads\audit-automation-final\templates\TATA Capital\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{019D89BE-707F-4A75-8E47-DC148871FDCB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE717224-2C0A-4275-84D7-18913E7DA024}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1500" yWindow="1500" windowWidth="13152" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Checklist" sheetId="8" r:id="rId1"/>
@@ -2321,6 +2321,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <_activity xmlns="0115396f-2e4a-4d2a-ba9c-df4d17cb71a2" xsi:nil="true"/>
@@ -2328,7 +2337,7 @@
 </p:properties>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100B89E9B38EF334341B754D8F8D6A719DA" ma:contentTypeVersion="16" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="fa1e129258e112aee4cf2e89d18a6563">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="0115396f-2e4a-4d2a-ba9c-df4d17cb71a2" xmlns:ns4="2bc29a05-2ca3-4765-9547-41c11361a102" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="c5debfbfacc377353d2d2775bb411679" ns3:_="" ns4:_="">
     <xsd:import namespace="0115396f-2e4a-4d2a-ba9c-df4d17cb71a2"/>
@@ -2567,16 +2576,15 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7A441EEC-55BA-46EA-90EF-FC0D7755347D}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D2F59799-9B83-49D0-A943-0DC9FFAB44BC}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
@@ -2593,7 +2601,7 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2DF47549-3EF2-4376-830A-0D6707ECCEB2}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -2610,12 +2618,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7A441EEC-55BA-46EA-90EF-FC0D7755347D}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>